--- a/Pruebas calificadas/COLEGIO-ABEL-RODRIGUEZ-CESPEDES-(IED)-701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-ABEL-RODRIGUEZ-CESPEDES-(IED)-701_CALIFICADO.xlsx
@@ -2364,9 +2364,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -9924,9 +9924,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -10173,9 +10173,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -10426,9 +10426,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -10928,9 +10928,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -11434,9 +11434,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -11687,9 +11687,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -11936,9 +11936,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -12189,9 +12189,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -12693,9 +12693,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -12946,9 +12946,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -13199,9 +13199,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -13452,9 +13452,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -13705,9 +13705,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -14203,9 +14203,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -14709,9 +14709,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -14962,9 +14962,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -15215,9 +15215,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -15468,9 +15468,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -15721,9 +15721,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -15974,9 +15974,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -16227,9 +16227,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -16480,9 +16480,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -17492,9 +17492,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -18251,9 +18251,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -18757,9 +18757,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-ABEL-RODRIGUEZ-CESPEDES-(IED)-701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-ABEL-RODRIGUEZ-CESPEDES-(IED)-701_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -1558,11 +1546,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -1811,11 +1795,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -2064,11 +2044,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -2313,11 +2289,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -2566,11 +2538,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -2819,11 +2787,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -3072,11 +3036,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -3325,11 +3285,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -3578,11 +3534,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -3831,11 +3783,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -4080,11 +4028,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -4333,11 +4277,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -4574,11 +4514,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -4823,11 +4759,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -5076,11 +5008,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -5321,11 +5249,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -5574,11 +5498,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -5827,11 +5747,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -6080,11 +5996,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -6333,11 +6245,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -6586,11 +6494,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -6839,11 +6743,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -7092,11 +6992,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -7343,11 +7239,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -7596,11 +7488,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -7849,11 +7737,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -8102,11 +7986,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -8355,11 +8235,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -8608,11 +8484,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -8861,11 +8733,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -9114,11 +8982,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -9367,11 +9231,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -9620,11 +9480,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -9873,11 +9729,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -10122,11 +9974,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -10375,11 +10223,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -10628,11 +10472,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -10877,11 +10717,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -11130,11 +10966,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -11383,11 +11215,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -11636,11 +11464,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -11889,11 +11713,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -12138,11 +11958,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -12391,11 +12207,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -12642,11 +12454,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -12895,11 +12703,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -13148,11 +12952,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -13401,11 +13201,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -13654,11 +13450,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -13903,11 +13695,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -14152,11 +13940,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -14405,11 +14189,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -14658,11 +14438,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -14911,11 +14687,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -15164,11 +14936,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -15417,11 +15185,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -15670,11 +15434,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -15923,11 +15683,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -16176,11 +15932,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -16429,11 +16181,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -16682,11 +16430,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -16935,11 +16679,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -17188,11 +16928,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -17441,11 +17177,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -17694,11 +17426,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -17947,11 +17675,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -18200,11 +17924,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -18453,11 +18173,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
@@ -18706,11 +18422,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001801055</t>
